--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118969637</v>
+        <v>118970073</v>
       </c>
       <c r="B2" t="n">
-        <v>90529</v>
+        <v>79080</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         <v>478571</v>
       </c>
       <c r="R2" t="n">
-        <v>6954020</v>
+        <v>6954128</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118969797</v>
+        <v>118969637</v>
       </c>
       <c r="B3" t="n">
-        <v>79600</v>
+        <v>90529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478554</v>
+        <v>478571</v>
       </c>
       <c r="R3" t="n">
-        <v>6954024</v>
+        <v>6954020</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118970009</v>
+        <v>118969797</v>
       </c>
       <c r="B4" t="n">
-        <v>78228</v>
+        <v>79600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478597</v>
+        <v>478554</v>
       </c>
       <c r="R4" t="n">
-        <v>6954110</v>
+        <v>6954024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118969987</v>
+        <v>118970009</v>
       </c>
       <c r="B5" t="n">
         <v>78228</v>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478594</v>
+        <v>478597</v>
       </c>
       <c r="R5" t="n">
-        <v>6954105</v>
+        <v>6954110</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118970073</v>
+        <v>118969987</v>
       </c>
       <c r="B6" t="n">
-        <v>79080</v>
+        <v>78228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478571</v>
+        <v>478594</v>
       </c>
       <c r="R6" t="n">
-        <v>6954128</v>
+        <v>6954105</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,19 +1223,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118970064</v>
+        <v>118969605</v>
       </c>
       <c r="B7" t="n">
         <v>78491</v>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478578</v>
+        <v>478616</v>
       </c>
       <c r="R7" t="n">
-        <v>6954108</v>
+        <v>6954026</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,19 +1335,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118969605</v>
+        <v>118970064</v>
       </c>
       <c r="B8" t="n">
         <v>78491</v>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478616</v>
+        <v>478578</v>
       </c>
       <c r="R8" t="n">
-        <v>6954026</v>
+        <v>6954108</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,12 +1447,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186068</v>
+        <v>122186074</v>
       </c>
       <c r="B10" t="n">
-        <v>90797</v>
+        <v>96040</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478648</v>
+        <v>478574</v>
       </c>
       <c r="R10" t="n">
-        <v>6954030</v>
+        <v>6954036</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186129</v>
+        <v>122186112</v>
       </c>
       <c r="B11" t="n">
-        <v>79726</v>
+        <v>57527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478270</v>
+        <v>478385</v>
       </c>
       <c r="R11" t="n">
-        <v>6954768</v>
+        <v>6954495</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186069</v>
+        <v>122186129</v>
       </c>
       <c r="B12" t="n">
-        <v>97129</v>
+        <v>79726</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,25 +1777,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478619</v>
+        <v>478270</v>
       </c>
       <c r="R12" t="n">
-        <v>6954010</v>
+        <v>6954768</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186131</v>
+        <v>122186068</v>
       </c>
       <c r="B13" t="n">
-        <v>79263</v>
+        <v>90797</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478306</v>
+        <v>478648</v>
       </c>
       <c r="R13" t="n">
-        <v>6954783</v>
+        <v>6954030</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186074</v>
+        <v>122186071</v>
       </c>
       <c r="B14" t="n">
-        <v>96040</v>
+        <v>57485</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,38 +1981,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>990</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478574</v>
+        <v>478617</v>
       </c>
       <c r="R14" t="n">
-        <v>6954036</v>
+        <v>6954010</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2071,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186073</v>
+        <v>122186077</v>
       </c>
       <c r="B15" t="n">
-        <v>57527</v>
+        <v>97129</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,25 +2087,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478615</v>
+        <v>478526</v>
       </c>
       <c r="R15" t="n">
-        <v>6954027</v>
+        <v>6953974</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2173,10 +2177,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186132</v>
+        <v>122186080</v>
       </c>
       <c r="B16" t="n">
-        <v>78290</v>
+        <v>78381</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,21 +2193,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478306</v>
+        <v>478458</v>
       </c>
       <c r="R16" t="n">
-        <v>6954782</v>
+        <v>6954184</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2243,12 +2247,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2279,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186089</v>
+        <v>122186135</v>
       </c>
       <c r="B17" t="n">
-        <v>78381</v>
+        <v>57374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2295,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478467</v>
+        <v>478310</v>
       </c>
       <c r="R17" t="n">
-        <v>6954372</v>
+        <v>6954795</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2345,12 +2349,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186134</v>
+        <v>122186072</v>
       </c>
       <c r="B18" t="n">
-        <v>57485</v>
+        <v>90797</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2389,25 +2393,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478295</v>
+        <v>478577</v>
       </c>
       <c r="R18" t="n">
-        <v>6954784</v>
+        <v>6954027</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2447,12 +2451,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186077</v>
+        <v>122186073</v>
       </c>
       <c r="B19" t="n">
-        <v>97129</v>
+        <v>57527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,25 +2495,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478526</v>
+        <v>478615</v>
       </c>
       <c r="R19" t="n">
-        <v>6953974</v>
+        <v>6954027</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2581,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186070</v>
+        <v>122186089</v>
       </c>
       <c r="B20" t="n">
-        <v>57390</v>
+        <v>78381</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478610</v>
+        <v>478467</v>
       </c>
       <c r="R20" t="n">
-        <v>6954005</v>
+        <v>6954372</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2683,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186071</v>
+        <v>122186067</v>
       </c>
       <c r="B21" t="n">
-        <v>57485</v>
+        <v>90797</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2695,42 +2699,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478617</v>
+        <v>478696</v>
       </c>
       <c r="R21" t="n">
-        <v>6954010</v>
+        <v>6954019</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2789,10 +2789,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122186072</v>
+        <v>122186081</v>
       </c>
       <c r="B22" t="n">
-        <v>90797</v>
+        <v>57390</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2805,21 +2805,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478577</v>
+        <v>478413</v>
       </c>
       <c r="R22" t="n">
-        <v>6954027</v>
+        <v>6954437</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186080</v>
+        <v>122186070</v>
       </c>
       <c r="B23" t="n">
-        <v>78381</v>
+        <v>57390</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478458</v>
+        <v>478610</v>
       </c>
       <c r="R23" t="n">
-        <v>6954184</v>
+        <v>6954005</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122186078</v>
+        <v>122186134</v>
       </c>
       <c r="B24" t="n">
-        <v>57527</v>
+        <v>57485</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,25 +3005,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478486</v>
+        <v>478295</v>
       </c>
       <c r="R24" t="n">
-        <v>6954106</v>
+        <v>6954784</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3095,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122186135</v>
+        <v>122186114</v>
       </c>
       <c r="B25" t="n">
-        <v>57374</v>
+        <v>97129</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,25 +3107,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478310</v>
+        <v>478405</v>
       </c>
       <c r="R25" t="n">
-        <v>6954795</v>
+        <v>6954494</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3165,12 +3165,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122186081</v>
+        <v>122186069</v>
       </c>
       <c r="B26" t="n">
-        <v>57390</v>
+        <v>97129</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,25 +3209,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478413</v>
+        <v>478619</v>
       </c>
       <c r="R26" t="n">
-        <v>6954437</v>
+        <v>6954010</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186179</v>
+        <v>122186078</v>
       </c>
       <c r="B27" t="n">
-        <v>97129</v>
+        <v>57527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,25 +3311,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478474</v>
+        <v>478486</v>
       </c>
       <c r="R27" t="n">
-        <v>6954539</v>
+        <v>6954106</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3369,12 +3369,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3401,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122186067</v>
+        <v>122186132</v>
       </c>
       <c r="B28" t="n">
-        <v>90797</v>
+        <v>78290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478696</v>
+        <v>478306</v>
       </c>
       <c r="R28" t="n">
-        <v>6954019</v>
+        <v>6954782</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186112</v>
+        <v>122186131</v>
       </c>
       <c r="B29" t="n">
-        <v>57527</v>
+        <v>79263</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478385</v>
+        <v>478306</v>
       </c>
       <c r="R29" t="n">
-        <v>6954495</v>
+        <v>6954783</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3605,7 +3605,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122186114</v>
+        <v>122186179</v>
       </c>
       <c r="B30" t="n">
         <v>97129</v>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478405</v>
+        <v>478474</v>
       </c>
       <c r="R30" t="n">
-        <v>6954494</v>
+        <v>6954539</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186089</v>
+        <v>122186067</v>
       </c>
       <c r="B20" t="n">
-        <v>78381</v>
+        <v>90797</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478467</v>
+        <v>478696</v>
       </c>
       <c r="R20" t="n">
-        <v>6954372</v>
+        <v>6954019</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186067</v>
+        <v>122186089</v>
       </c>
       <c r="B21" t="n">
-        <v>90797</v>
+        <v>78381</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478696</v>
+        <v>478467</v>
       </c>
       <c r="R21" t="n">
-        <v>6954019</v>
+        <v>6954372</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122186133</v>
+        <v>122186073</v>
       </c>
       <c r="B9" t="n">
         <v>57527</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478327</v>
+        <v>478615</v>
       </c>
       <c r="R9" t="n">
-        <v>6954735</v>
+        <v>6954027</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186074</v>
+        <v>122186134</v>
       </c>
       <c r="B10" t="n">
-        <v>96040</v>
+        <v>57485</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>990</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478574</v>
+        <v>478295</v>
       </c>
       <c r="R10" t="n">
-        <v>6954036</v>
+        <v>6954784</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186112</v>
+        <v>122186080</v>
       </c>
       <c r="B11" t="n">
-        <v>57527</v>
+        <v>78382</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478385</v>
+        <v>478458</v>
       </c>
       <c r="R11" t="n">
-        <v>6954495</v>
+        <v>6954184</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186129</v>
+        <v>122186132</v>
       </c>
       <c r="B12" t="n">
-        <v>79726</v>
+        <v>78291</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478270</v>
+        <v>478306</v>
       </c>
       <c r="R12" t="n">
-        <v>6954768</v>
+        <v>6954782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186068</v>
+        <v>122186070</v>
       </c>
       <c r="B13" t="n">
-        <v>90797</v>
+        <v>57390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478648</v>
+        <v>478610</v>
       </c>
       <c r="R13" t="n">
-        <v>6954030</v>
+        <v>6954005</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186071</v>
+        <v>122186135</v>
       </c>
       <c r="B14" t="n">
-        <v>57485</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,20 +1981,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2002,21 +2002,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478617</v>
+        <v>478310</v>
       </c>
       <c r="R14" t="n">
-        <v>6954010</v>
+        <v>6954795</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2043,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186077</v>
+        <v>122186069</v>
       </c>
       <c r="B15" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478526</v>
+        <v>478619</v>
       </c>
       <c r="R15" t="n">
-        <v>6953974</v>
+        <v>6954010</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2177,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186080</v>
+        <v>122186077</v>
       </c>
       <c r="B16" t="n">
-        <v>78381</v>
+        <v>97139</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,25 +2185,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478458</v>
+        <v>478526</v>
       </c>
       <c r="R16" t="n">
-        <v>6954184</v>
+        <v>6953974</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2279,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186135</v>
+        <v>122186071</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>57485</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,20 +2287,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2312,17 +2308,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478310</v>
+        <v>478617</v>
       </c>
       <c r="R17" t="n">
-        <v>6954795</v>
+        <v>6954010</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186072</v>
+        <v>122186179</v>
       </c>
       <c r="B18" t="n">
-        <v>90797</v>
+        <v>97139</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,25 +2393,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478577</v>
+        <v>478474</v>
       </c>
       <c r="R18" t="n">
-        <v>6954027</v>
+        <v>6954539</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2451,12 +2451,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186073</v>
+        <v>122186074</v>
       </c>
       <c r="B19" t="n">
-        <v>57527</v>
+        <v>96050</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,25 +2495,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>990</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478615</v>
+        <v>478574</v>
       </c>
       <c r="R19" t="n">
-        <v>6954027</v>
+        <v>6954036</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186067</v>
+        <v>122186078</v>
       </c>
       <c r="B20" t="n">
-        <v>90797</v>
+        <v>57527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478696</v>
+        <v>478486</v>
       </c>
       <c r="R20" t="n">
-        <v>6954019</v>
+        <v>6954106</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186089</v>
+        <v>122186068</v>
       </c>
       <c r="B21" t="n">
-        <v>78381</v>
+        <v>90807</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478467</v>
+        <v>478648</v>
       </c>
       <c r="R21" t="n">
-        <v>6954372</v>
+        <v>6954030</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2789,10 +2789,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122186081</v>
+        <v>122186114</v>
       </c>
       <c r="B22" t="n">
-        <v>57390</v>
+        <v>97139</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,25 +2801,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478413</v>
+        <v>478405</v>
       </c>
       <c r="R22" t="n">
-        <v>6954437</v>
+        <v>6954494</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186070</v>
+        <v>122186112</v>
       </c>
       <c r="B23" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478610</v>
+        <v>478385</v>
       </c>
       <c r="R23" t="n">
-        <v>6954005</v>
+        <v>6954495</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122186134</v>
+        <v>122186089</v>
       </c>
       <c r="B24" t="n">
-        <v>57485</v>
+        <v>78382</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,25 +3005,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478295</v>
+        <v>478467</v>
       </c>
       <c r="R24" t="n">
-        <v>6954784</v>
+        <v>6954372</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3095,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122186114</v>
+        <v>122186133</v>
       </c>
       <c r="B25" t="n">
-        <v>97129</v>
+        <v>57527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,25 +3107,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478405</v>
+        <v>478327</v>
       </c>
       <c r="R25" t="n">
-        <v>6954494</v>
+        <v>6954735</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3165,12 +3165,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122186069</v>
+        <v>122186081</v>
       </c>
       <c r="B26" t="n">
-        <v>97129</v>
+        <v>57390</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,25 +3209,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478619</v>
+        <v>478413</v>
       </c>
       <c r="R26" t="n">
-        <v>6954010</v>
+        <v>6954437</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186078</v>
+        <v>122186131</v>
       </c>
       <c r="B27" t="n">
-        <v>57527</v>
+        <v>79264</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3315,21 +3315,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478486</v>
+        <v>478306</v>
       </c>
       <c r="R27" t="n">
-        <v>6954106</v>
+        <v>6954783</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3369,12 +3369,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3401,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122186132</v>
+        <v>122186072</v>
       </c>
       <c r="B28" t="n">
-        <v>78290</v>
+        <v>90807</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478306</v>
+        <v>478577</v>
       </c>
       <c r="R28" t="n">
-        <v>6954782</v>
+        <v>6954027</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186131</v>
+        <v>122186129</v>
       </c>
       <c r="B29" t="n">
-        <v>79263</v>
+        <v>79727</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478306</v>
+        <v>478270</v>
       </c>
       <c r="R29" t="n">
-        <v>6954783</v>
+        <v>6954768</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122186179</v>
+        <v>122186067</v>
       </c>
       <c r="B30" t="n">
-        <v>97129</v>
+        <v>90807</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3617,25 +3617,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478474</v>
+        <v>478696</v>
       </c>
       <c r="R30" t="n">
-        <v>6954539</v>
+        <v>6954019</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122186073</v>
+        <v>122186129</v>
       </c>
       <c r="B9" t="n">
-        <v>57527</v>
+        <v>79727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478615</v>
+        <v>478270</v>
       </c>
       <c r="R9" t="n">
-        <v>6954027</v>
+        <v>6954768</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186134</v>
+        <v>122186073</v>
       </c>
       <c r="B10" t="n">
-        <v>57485</v>
+        <v>57527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478295</v>
+        <v>478615</v>
       </c>
       <c r="R10" t="n">
-        <v>6954784</v>
+        <v>6954027</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186132</v>
+        <v>122186078</v>
       </c>
       <c r="B12" t="n">
-        <v>78291</v>
+        <v>57527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478306</v>
+        <v>478486</v>
       </c>
       <c r="R12" t="n">
-        <v>6954782</v>
+        <v>6954106</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186070</v>
+        <v>122186068</v>
       </c>
       <c r="B13" t="n">
-        <v>57390</v>
+        <v>90807</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478610</v>
+        <v>478648</v>
       </c>
       <c r="R13" t="n">
-        <v>6954005</v>
+        <v>6954030</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186135</v>
+        <v>122186081</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478310</v>
+        <v>478413</v>
       </c>
       <c r="R14" t="n">
-        <v>6954795</v>
+        <v>6954437</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186069</v>
+        <v>122186067</v>
       </c>
       <c r="B15" t="n">
-        <v>97139</v>
+        <v>90807</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,25 +2083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478619</v>
+        <v>478696</v>
       </c>
       <c r="R15" t="n">
-        <v>6954010</v>
+        <v>6954019</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186077</v>
+        <v>122186112</v>
       </c>
       <c r="B16" t="n">
-        <v>97139</v>
+        <v>57527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,25 +2185,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478526</v>
+        <v>478385</v>
       </c>
       <c r="R16" t="n">
-        <v>6953974</v>
+        <v>6954495</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186071</v>
+        <v>122186133</v>
       </c>
       <c r="B17" t="n">
-        <v>57485</v>
+        <v>57527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,42 +2287,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478617</v>
+        <v>478327</v>
       </c>
       <c r="R17" t="n">
-        <v>6954010</v>
+        <v>6954735</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2349,12 +2345,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186179</v>
+        <v>122186134</v>
       </c>
       <c r="B18" t="n">
-        <v>97139</v>
+        <v>57485</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478474</v>
+        <v>478295</v>
       </c>
       <c r="R18" t="n">
-        <v>6954539</v>
+        <v>6954784</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2585,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186078</v>
+        <v>122186114</v>
       </c>
       <c r="B20" t="n">
-        <v>57527</v>
+        <v>97139</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,25 +2593,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2625,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478486</v>
+        <v>478405</v>
       </c>
       <c r="R20" t="n">
-        <v>6954106</v>
+        <v>6954494</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2687,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186068</v>
+        <v>122186179</v>
       </c>
       <c r="B21" t="n">
-        <v>90807</v>
+        <v>97139</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,25 +2695,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2727,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478648</v>
+        <v>478474</v>
       </c>
       <c r="R21" t="n">
-        <v>6954030</v>
+        <v>6954539</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2757,12 +2753,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2789,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122186114</v>
+        <v>122186071</v>
       </c>
       <c r="B22" t="n">
-        <v>97139</v>
+        <v>57485</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2805,34 +2801,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478405</v>
+        <v>478617</v>
       </c>
       <c r="R22" t="n">
-        <v>6954494</v>
+        <v>6954010</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186112</v>
+        <v>122186089</v>
       </c>
       <c r="B23" t="n">
-        <v>57527</v>
+        <v>78382</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478385</v>
+        <v>478467</v>
       </c>
       <c r="R23" t="n">
-        <v>6954495</v>
+        <v>6954372</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122186089</v>
+        <v>122186070</v>
       </c>
       <c r="B24" t="n">
-        <v>78382</v>
+        <v>57390</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478467</v>
+        <v>478610</v>
       </c>
       <c r="R24" t="n">
-        <v>6954372</v>
+        <v>6954005</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3095,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122186133</v>
+        <v>122186135</v>
       </c>
       <c r="B25" t="n">
-        <v>57527</v>
+        <v>57374</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478327</v>
+        <v>478310</v>
       </c>
       <c r="R25" t="n">
-        <v>6954735</v>
+        <v>6954795</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122186081</v>
+        <v>122186069</v>
       </c>
       <c r="B26" t="n">
-        <v>57390</v>
+        <v>97139</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,25 +3209,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478413</v>
+        <v>478619</v>
       </c>
       <c r="R26" t="n">
-        <v>6954437</v>
+        <v>6954010</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186131</v>
+        <v>122186077</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>97139</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,25 +3311,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478306</v>
+        <v>478526</v>
       </c>
       <c r="R27" t="n">
-        <v>6954783</v>
+        <v>6953974</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3369,12 +3369,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186129</v>
+        <v>122186132</v>
       </c>
       <c r="B29" t="n">
-        <v>79727</v>
+        <v>78291</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478270</v>
+        <v>478306</v>
       </c>
       <c r="R29" t="n">
-        <v>6954768</v>
+        <v>6954782</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122186067</v>
+        <v>122186131</v>
       </c>
       <c r="B30" t="n">
-        <v>90807</v>
+        <v>79264</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3621,21 +3621,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478696</v>
+        <v>478306</v>
       </c>
       <c r="R30" t="n">
-        <v>6954019</v>
+        <v>6954783</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186073</v>
+        <v>122186080</v>
       </c>
       <c r="B10" t="n">
-        <v>57527</v>
+        <v>78382</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478615</v>
+        <v>478458</v>
       </c>
       <c r="R10" t="n">
-        <v>6954027</v>
+        <v>6954184</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186080</v>
+        <v>122186073</v>
       </c>
       <c r="B11" t="n">
-        <v>78382</v>
+        <v>57527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478458</v>
+        <v>478615</v>
       </c>
       <c r="R11" t="n">
-        <v>6954184</v>
+        <v>6954027</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122186129</v>
+        <v>122186067</v>
       </c>
       <c r="B9" t="n">
-        <v>79727</v>
+        <v>90819</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478270</v>
+        <v>478696</v>
       </c>
       <c r="R9" t="n">
-        <v>6954768</v>
+        <v>6954019</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186080</v>
+        <v>122186074</v>
       </c>
       <c r="B10" t="n">
-        <v>78382</v>
+        <v>96062</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478458</v>
+        <v>478574</v>
       </c>
       <c r="R10" t="n">
-        <v>6954184</v>
+        <v>6954036</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186073</v>
+        <v>122186080</v>
       </c>
       <c r="B11" t="n">
-        <v>57527</v>
+        <v>78387</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478615</v>
+        <v>478458</v>
       </c>
       <c r="R11" t="n">
-        <v>6954027</v>
+        <v>6954184</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186078</v>
+        <v>122186179</v>
       </c>
       <c r="B12" t="n">
-        <v>57527</v>
+        <v>97151</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,25 +1777,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478486</v>
+        <v>478474</v>
       </c>
       <c r="R12" t="n">
-        <v>6954106</v>
+        <v>6954539</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186068</v>
+        <v>122186071</v>
       </c>
       <c r="B13" t="n">
-        <v>90807</v>
+        <v>57490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,38 +1879,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478648</v>
+        <v>478617</v>
       </c>
       <c r="R13" t="n">
-        <v>6954030</v>
+        <v>6954010</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1969,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186081</v>
+        <v>122186070</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478413</v>
+        <v>478610</v>
       </c>
       <c r="R14" t="n">
-        <v>6954437</v>
+        <v>6954005</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2071,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186067</v>
+        <v>122186072</v>
       </c>
       <c r="B15" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478696</v>
+        <v>478577</v>
       </c>
       <c r="R15" t="n">
-        <v>6954019</v>
+        <v>6954027</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2173,10 +2177,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186112</v>
+        <v>122186069</v>
       </c>
       <c r="B16" t="n">
-        <v>57527</v>
+        <v>97151</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,25 +2189,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478385</v>
+        <v>478619</v>
       </c>
       <c r="R16" t="n">
-        <v>6954495</v>
+        <v>6954010</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,10 +2279,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186133</v>
+        <v>122186135</v>
       </c>
       <c r="B17" t="n">
-        <v>57527</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2295,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478327</v>
+        <v>478310</v>
       </c>
       <c r="R17" t="n">
-        <v>6954735</v>
+        <v>6954795</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186134</v>
+        <v>122186078</v>
       </c>
       <c r="B18" t="n">
-        <v>57485</v>
+        <v>57532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2389,25 +2393,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478295</v>
+        <v>478486</v>
       </c>
       <c r="R18" t="n">
-        <v>6954784</v>
+        <v>6954106</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2447,12 +2451,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186074</v>
+        <v>122186073</v>
       </c>
       <c r="B19" t="n">
-        <v>96050</v>
+        <v>57532</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,25 +2495,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>990</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478574</v>
+        <v>478615</v>
       </c>
       <c r="R19" t="n">
-        <v>6954036</v>
+        <v>6954027</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2581,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186114</v>
+        <v>122186134</v>
       </c>
       <c r="B20" t="n">
-        <v>97139</v>
+        <v>57490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478405</v>
+        <v>478295</v>
       </c>
       <c r="R20" t="n">
-        <v>6954494</v>
+        <v>6954784</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2651,12 +2655,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186179</v>
+        <v>122186114</v>
       </c>
       <c r="B21" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478474</v>
+        <v>478405</v>
       </c>
       <c r="R21" t="n">
-        <v>6954539</v>
+        <v>6954494</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2753,12 +2757,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2789,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122186071</v>
+        <v>122186132</v>
       </c>
       <c r="B22" t="n">
-        <v>57485</v>
+        <v>78296</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2797,42 +2801,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478617</v>
+        <v>478306</v>
       </c>
       <c r="R22" t="n">
-        <v>6954010</v>
+        <v>6954782</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186089</v>
+        <v>122186112</v>
       </c>
       <c r="B23" t="n">
-        <v>78382</v>
+        <v>57532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478467</v>
+        <v>478385</v>
       </c>
       <c r="R23" t="n">
-        <v>6954372</v>
+        <v>6954495</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122186070</v>
+        <v>122186089</v>
       </c>
       <c r="B24" t="n">
-        <v>57390</v>
+        <v>78387</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478610</v>
+        <v>478467</v>
       </c>
       <c r="R24" t="n">
-        <v>6954005</v>
+        <v>6954372</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3095,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122186135</v>
+        <v>122186129</v>
       </c>
       <c r="B25" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478310</v>
+        <v>478270</v>
       </c>
       <c r="R25" t="n">
-        <v>6954795</v>
+        <v>6954768</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122186069</v>
+        <v>122186068</v>
       </c>
       <c r="B26" t="n">
-        <v>97139</v>
+        <v>90819</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,25 +3209,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478619</v>
+        <v>478648</v>
       </c>
       <c r="R26" t="n">
-        <v>6954010</v>
+        <v>6954030</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186077</v>
+        <v>122186131</v>
       </c>
       <c r="B27" t="n">
-        <v>97139</v>
+        <v>79269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,25 +3311,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478526</v>
+        <v>478306</v>
       </c>
       <c r="R27" t="n">
-        <v>6953974</v>
+        <v>6954783</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3369,12 +3369,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3401,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122186072</v>
+        <v>122186077</v>
       </c>
       <c r="B28" t="n">
-        <v>90807</v>
+        <v>97151</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,25 +3413,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478577</v>
+        <v>478526</v>
       </c>
       <c r="R28" t="n">
-        <v>6954027</v>
+        <v>6953974</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186132</v>
+        <v>122186133</v>
       </c>
       <c r="B29" t="n">
-        <v>78291</v>
+        <v>57532</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478306</v>
+        <v>478327</v>
       </c>
       <c r="R29" t="n">
-        <v>6954782</v>
+        <v>6954735</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122186131</v>
+        <v>122186081</v>
       </c>
       <c r="B30" t="n">
-        <v>79264</v>
+        <v>57395</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3621,21 +3621,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478306</v>
+        <v>478413</v>
       </c>
       <c r="R30" t="n">
-        <v>6954783</v>
+        <v>6954437</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122186067</v>
+        <v>122186081</v>
       </c>
       <c r="B9" t="n">
-        <v>90819</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478696</v>
+        <v>478413</v>
       </c>
       <c r="R9" t="n">
-        <v>6954019</v>
+        <v>6954437</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186074</v>
+        <v>122186070</v>
       </c>
       <c r="B10" t="n">
-        <v>96062</v>
+        <v>57395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>990</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478574</v>
+        <v>478610</v>
       </c>
       <c r="R10" t="n">
-        <v>6954036</v>
+        <v>6954005</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186080</v>
+        <v>122186135</v>
       </c>
       <c r="B11" t="n">
-        <v>78387</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478458</v>
+        <v>478310</v>
       </c>
       <c r="R11" t="n">
-        <v>6954184</v>
+        <v>6954795</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186179</v>
+        <v>122186069</v>
       </c>
       <c r="B12" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478474</v>
+        <v>478619</v>
       </c>
       <c r="R12" t="n">
-        <v>6954539</v>
+        <v>6954010</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186071</v>
+        <v>122186112</v>
       </c>
       <c r="B13" t="n">
-        <v>57490</v>
+        <v>57532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,42 +1879,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478617</v>
+        <v>478385</v>
       </c>
       <c r="R13" t="n">
-        <v>6954010</v>
+        <v>6954495</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1973,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186070</v>
+        <v>122186132</v>
       </c>
       <c r="B14" t="n">
-        <v>57395</v>
+        <v>78296</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478610</v>
+        <v>478306</v>
       </c>
       <c r="R14" t="n">
-        <v>6954005</v>
+        <v>6954782</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2043,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186072</v>
+        <v>122186077</v>
       </c>
       <c r="B15" t="n">
-        <v>90819</v>
+        <v>97156</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,25 +2083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2115,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478577</v>
+        <v>478526</v>
       </c>
       <c r="R15" t="n">
-        <v>6954027</v>
+        <v>6953974</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2177,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186069</v>
+        <v>122186072</v>
       </c>
       <c r="B16" t="n">
-        <v>97151</v>
+        <v>90826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,25 +2185,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478619</v>
+        <v>478577</v>
       </c>
       <c r="R16" t="n">
-        <v>6954010</v>
+        <v>6954027</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2279,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186135</v>
+        <v>122186129</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2319,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478310</v>
+        <v>478270</v>
       </c>
       <c r="R17" t="n">
-        <v>6954795</v>
+        <v>6954768</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2381,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186078</v>
+        <v>122186179</v>
       </c>
       <c r="B18" t="n">
-        <v>57532</v>
+        <v>97156</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,25 +2389,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478486</v>
+        <v>478474</v>
       </c>
       <c r="R18" t="n">
-        <v>6954106</v>
+        <v>6954539</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2451,12 +2447,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186073</v>
+        <v>122186080</v>
       </c>
       <c r="B19" t="n">
-        <v>57532</v>
+        <v>78387</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478615</v>
+        <v>478458</v>
       </c>
       <c r="R19" t="n">
-        <v>6954027</v>
+        <v>6954184</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2585,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186134</v>
+        <v>122186071</v>
       </c>
       <c r="B20" t="n">
         <v>57490</v>
@@ -2618,17 +2614,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478295</v>
+        <v>478617</v>
       </c>
       <c r="R20" t="n">
-        <v>6954784</v>
+        <v>6954010</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,7 +2690,7 @@
         <v>122186114</v>
       </c>
       <c r="B21" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2789,10 +2789,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122186132</v>
+        <v>122186073</v>
       </c>
       <c r="B22" t="n">
-        <v>78296</v>
+        <v>57532</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2805,21 +2805,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478306</v>
+        <v>478615</v>
       </c>
       <c r="R22" t="n">
-        <v>6954782</v>
+        <v>6954027</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186112</v>
+        <v>122186074</v>
       </c>
       <c r="B23" t="n">
-        <v>57532</v>
+        <v>96067</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,25 +2903,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>990</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478385</v>
+        <v>478574</v>
       </c>
       <c r="R23" t="n">
-        <v>6954495</v>
+        <v>6954036</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122186089</v>
+        <v>122186068</v>
       </c>
       <c r="B24" t="n">
-        <v>78387</v>
+        <v>90826</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478467</v>
+        <v>478648</v>
       </c>
       <c r="R24" t="n">
-        <v>6954372</v>
+        <v>6954030</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3095,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122186129</v>
+        <v>122186133</v>
       </c>
       <c r="B25" t="n">
-        <v>79732</v>
+        <v>57532</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478270</v>
+        <v>478327</v>
       </c>
       <c r="R25" t="n">
-        <v>6954768</v>
+        <v>6954735</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122186068</v>
+        <v>122186078</v>
       </c>
       <c r="B26" t="n">
-        <v>90819</v>
+        <v>57532</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,21 +3213,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478648</v>
+        <v>478486</v>
       </c>
       <c r="R26" t="n">
-        <v>6954030</v>
+        <v>6954106</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186131</v>
+        <v>122186134</v>
       </c>
       <c r="B27" t="n">
-        <v>79269</v>
+        <v>57490</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,25 +3311,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478306</v>
+        <v>478295</v>
       </c>
       <c r="R27" t="n">
-        <v>6954783</v>
+        <v>6954784</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122186077</v>
+        <v>122186067</v>
       </c>
       <c r="B28" t="n">
-        <v>97151</v>
+        <v>90826</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,25 +3413,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478526</v>
+        <v>478696</v>
       </c>
       <c r="R28" t="n">
-        <v>6953974</v>
+        <v>6954019</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186133</v>
+        <v>122186089</v>
       </c>
       <c r="B29" t="n">
-        <v>57532</v>
+        <v>78387</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478327</v>
+        <v>478467</v>
       </c>
       <c r="R29" t="n">
-        <v>6954735</v>
+        <v>6954372</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3605,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122186081</v>
+        <v>122186131</v>
       </c>
       <c r="B30" t="n">
-        <v>57395</v>
+        <v>79269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3621,21 +3621,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478413</v>
+        <v>478306</v>
       </c>
       <c r="R30" t="n">
-        <v>6954437</v>
+        <v>6954783</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186069</v>
+        <v>122186112</v>
       </c>
       <c r="B12" t="n">
-        <v>97156</v>
+        <v>57532</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,25 +1777,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478619</v>
+        <v>478385</v>
       </c>
       <c r="R12" t="n">
-        <v>6954010</v>
+        <v>6954495</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186112</v>
+        <v>122186069</v>
       </c>
       <c r="B13" t="n">
-        <v>57532</v>
+        <v>97156</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478385</v>
+        <v>478619</v>
       </c>
       <c r="R13" t="n">
-        <v>6954495</v>
+        <v>6954010</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186112</v>
+        <v>122186069</v>
       </c>
       <c r="B12" t="n">
-        <v>57532</v>
+        <v>97156</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,25 +1777,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478385</v>
+        <v>478619</v>
       </c>
       <c r="R12" t="n">
-        <v>6954495</v>
+        <v>6954010</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186069</v>
+        <v>122186112</v>
       </c>
       <c r="B13" t="n">
-        <v>97156</v>
+        <v>57532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478619</v>
+        <v>478385</v>
       </c>
       <c r="R13" t="n">
-        <v>6954010</v>
+        <v>6954495</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122186081</v>
+        <v>122186132</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>78297</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>353</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478413</v>
+        <v>478306</v>
       </c>
       <c r="R9" t="n">
-        <v>6954437</v>
+        <v>6954782</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,12 +1524,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186070</v>
+        <v>122186089</v>
       </c>
       <c r="B10" t="n">
-        <v>57395</v>
+        <v>78388</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1572,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6446</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478610</v>
+        <v>478467</v>
       </c>
       <c r="R10" t="n">
-        <v>6954005</v>
+        <v>6954372</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186135</v>
+        <v>122186067</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1669,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478310</v>
+        <v>478696</v>
       </c>
       <c r="R11" t="n">
-        <v>6954795</v>
+        <v>6954019</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1733,12 +1718,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186069</v>
+        <v>122186070</v>
       </c>
       <c r="B12" t="n">
-        <v>97156</v>
+        <v>57395</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,25 +1762,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478619</v>
+        <v>478610</v>
       </c>
       <c r="R12" t="n">
-        <v>6954010</v>
+        <v>6954005</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1867,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186112</v>
+        <v>122186129</v>
       </c>
       <c r="B13" t="n">
-        <v>57532</v>
+        <v>79733</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1863,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478385</v>
+        <v>478270</v>
       </c>
       <c r="R13" t="n">
-        <v>6954495</v>
+        <v>6954768</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,12 +1912,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186132</v>
+        <v>122186179</v>
       </c>
       <c r="B14" t="n">
-        <v>78296</v>
+        <v>97165</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,25 +1956,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478306</v>
+        <v>478474</v>
       </c>
       <c r="R14" t="n">
-        <v>6954782</v>
+        <v>6954539</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2071,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186077</v>
+        <v>122186071</v>
       </c>
       <c r="B15" t="n">
-        <v>97156</v>
+        <v>57490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,34 +2057,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>103031</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478526</v>
+        <v>478617</v>
       </c>
       <c r="R15" t="n">
-        <v>6953974</v>
+        <v>6954010</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2173,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186072</v>
+        <v>122186069</v>
       </c>
       <c r="B16" t="n">
-        <v>90826</v>
+        <v>97165</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,25 +2154,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478577</v>
+        <v>478619</v>
       </c>
       <c r="R16" t="n">
-        <v>6954027</v>
+        <v>6954010</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186129</v>
+        <v>122186133</v>
       </c>
       <c r="B17" t="n">
-        <v>79732</v>
+        <v>57532</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2255,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478270</v>
+        <v>478327</v>
       </c>
       <c r="R17" t="n">
-        <v>6954768</v>
+        <v>6954735</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186179</v>
+        <v>122186114</v>
       </c>
       <c r="B18" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2395,11 +2354,6 @@
       <c r="E18" t="n">
         <v>221945</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -2417,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478474</v>
+        <v>478405</v>
       </c>
       <c r="R18" t="n">
-        <v>6954539</v>
+        <v>6954494</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2447,12 +2401,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186080</v>
+        <v>122186068</v>
       </c>
       <c r="B19" t="n">
-        <v>78387</v>
+        <v>90831</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2449,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478458</v>
+        <v>478648</v>
       </c>
       <c r="R19" t="n">
-        <v>6954184</v>
+        <v>6954030</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2581,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186071</v>
+        <v>122186073</v>
       </c>
       <c r="B20" t="n">
-        <v>57490</v>
+        <v>57532</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,42 +2542,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478617</v>
+        <v>478615</v>
       </c>
       <c r="R20" t="n">
-        <v>6954010</v>
+        <v>6954027</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2687,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186114</v>
+        <v>122186080</v>
       </c>
       <c r="B21" t="n">
-        <v>97156</v>
+        <v>78388</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,25 +2639,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6446</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2727,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478405</v>
+        <v>478458</v>
       </c>
       <c r="R21" t="n">
-        <v>6954494</v>
+        <v>6954184</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2789,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122186073</v>
+        <v>122186072</v>
       </c>
       <c r="B22" t="n">
-        <v>57532</v>
+        <v>90831</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2805,21 +2740,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2829,7 +2759,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478615</v>
+        <v>478577</v>
       </c>
       <c r="R22" t="n">
         <v>6954027</v>
@@ -2891,10 +2821,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186074</v>
+        <v>122186078</v>
       </c>
       <c r="B23" t="n">
-        <v>96067</v>
+        <v>57532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,25 +2833,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>990</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Liten hornflikmossa</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2931,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478574</v>
+        <v>478486</v>
       </c>
       <c r="R23" t="n">
-        <v>6954036</v>
+        <v>6954106</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2993,10 +2918,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122186068</v>
+        <v>122186077</v>
       </c>
       <c r="B24" t="n">
-        <v>90826</v>
+        <v>97165</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,25 +2930,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +2953,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478648</v>
+        <v>478526</v>
       </c>
       <c r="R24" t="n">
-        <v>6954030</v>
+        <v>6953974</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3095,10 +3015,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122186133</v>
+        <v>122186074</v>
       </c>
       <c r="B25" t="n">
-        <v>57532</v>
+        <v>96076</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,25 +3027,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>990</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478327</v>
+        <v>478574</v>
       </c>
       <c r="R25" t="n">
-        <v>6954735</v>
+        <v>6954036</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3165,12 +3080,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3197,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122186078</v>
+        <v>122186081</v>
       </c>
       <c r="B26" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,21 +3128,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3147,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478486</v>
+        <v>478413</v>
       </c>
       <c r="R26" t="n">
-        <v>6954106</v>
+        <v>6954437</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3299,10 +3209,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186134</v>
+        <v>122186131</v>
       </c>
       <c r="B27" t="n">
-        <v>57490</v>
+        <v>79270</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,25 +3221,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3339,10 +3244,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478295</v>
+        <v>478306</v>
       </c>
       <c r="R27" t="n">
-        <v>6954784</v>
+        <v>6954783</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3401,10 +3306,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122186067</v>
+        <v>122186134</v>
       </c>
       <c r="B28" t="n">
-        <v>90826</v>
+        <v>57490</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,25 +3318,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>103031</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3441,10 +3341,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478696</v>
+        <v>478295</v>
       </c>
       <c r="R28" t="n">
-        <v>6954019</v>
+        <v>6954784</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3471,12 +3371,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3403,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186089</v>
+        <v>122186112</v>
       </c>
       <c r="B29" t="n">
-        <v>78387</v>
+        <v>57532</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,21 +3419,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3438,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478467</v>
+        <v>478385</v>
       </c>
       <c r="R29" t="n">
-        <v>6954372</v>
+        <v>6954495</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3605,10 +3500,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122186131</v>
+        <v>122186135</v>
       </c>
       <c r="B30" t="n">
-        <v>79269</v>
+        <v>57379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3621,21 +3516,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3535,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478306</v>
+        <v>478310</v>
       </c>
       <c r="R30" t="n">
-        <v>6954783</v>
+        <v>6954795</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186179</v>
+        <v>122186071</v>
       </c>
       <c r="B14" t="n">
-        <v>97165</v>
+        <v>57490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,29 +1960,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478474</v>
+        <v>478617</v>
       </c>
       <c r="R14" t="n">
-        <v>6954539</v>
+        <v>6954010</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2009,12 +2013,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186071</v>
+        <v>122186069</v>
       </c>
       <c r="B15" t="n">
-        <v>57490</v>
+        <v>97165</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,30 +2061,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>221945</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478617</v>
+        <v>478619</v>
       </c>
       <c r="R15" t="n">
         <v>6954010</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186069</v>
+        <v>122186179</v>
       </c>
       <c r="B16" t="n">
         <v>97165</v>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478619</v>
+        <v>478474</v>
       </c>
       <c r="R16" t="n">
-        <v>6954010</v>
+        <v>6954539</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2627,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186080</v>
+        <v>122186078</v>
       </c>
       <c r="B21" t="n">
-        <v>78388</v>
+        <v>57532</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,16 +2643,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478458</v>
+        <v>478486</v>
       </c>
       <c r="R21" t="n">
-        <v>6954184</v>
+        <v>6954106</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2821,10 +2821,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186078</v>
+        <v>122186080</v>
       </c>
       <c r="B23" t="n">
-        <v>57532</v>
+        <v>78388</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2837,16 +2837,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478486</v>
+        <v>478458</v>
       </c>
       <c r="R23" t="n">
-        <v>6954106</v>
+        <v>6954184</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186070</v>
+        <v>122186129</v>
       </c>
       <c r="B12" t="n">
-        <v>57395</v>
+        <v>79733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478610</v>
+        <v>478270</v>
       </c>
       <c r="R12" t="n">
-        <v>6954005</v>
+        <v>6954768</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186129</v>
+        <v>122186070</v>
       </c>
       <c r="B13" t="n">
-        <v>79733</v>
+        <v>57395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478270</v>
+        <v>478610</v>
       </c>
       <c r="R13" t="n">
-        <v>6954768</v>
+        <v>6954005</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2627,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186078</v>
+        <v>122186080</v>
       </c>
       <c r="B21" t="n">
-        <v>57532</v>
+        <v>78388</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,16 +2643,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478486</v>
+        <v>478458</v>
       </c>
       <c r="R21" t="n">
-        <v>6954106</v>
+        <v>6954184</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2821,10 +2821,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186080</v>
+        <v>122186078</v>
       </c>
       <c r="B23" t="n">
-        <v>78388</v>
+        <v>57532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2837,16 +2837,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478458</v>
+        <v>478486</v>
       </c>
       <c r="R23" t="n">
-        <v>6954184</v>
+        <v>6954106</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122186132</v>
+        <v>122186089</v>
       </c>
       <c r="B9" t="n">
-        <v>78297</v>
+        <v>78392</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,16 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478306</v>
+        <v>478467</v>
       </c>
       <c r="R9" t="n">
-        <v>6954782</v>
+        <v>6954372</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1524,12 +1529,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186089</v>
+        <v>122186067</v>
       </c>
       <c r="B10" t="n">
-        <v>78388</v>
+        <v>90844</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,16 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478467</v>
+        <v>478696</v>
       </c>
       <c r="R10" t="n">
-        <v>6954372</v>
+        <v>6954019</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1653,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186067</v>
+        <v>122186132</v>
       </c>
       <c r="B11" t="n">
-        <v>90831</v>
+        <v>78301</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,16 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>353</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478696</v>
+        <v>478306</v>
       </c>
       <c r="R11" t="n">
-        <v>6954019</v>
+        <v>6954782</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,12 +1733,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186129</v>
+        <v>122186133</v>
       </c>
       <c r="B12" t="n">
-        <v>79733</v>
+        <v>57536</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,16 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478270</v>
+        <v>478327</v>
       </c>
       <c r="R12" t="n">
-        <v>6954768</v>
+        <v>6954735</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186070</v>
+        <v>122186068</v>
       </c>
       <c r="B13" t="n">
-        <v>57395</v>
+        <v>90844</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,16 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478610</v>
+        <v>478648</v>
       </c>
       <c r="R13" t="n">
-        <v>6954005</v>
+        <v>6954030</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1944,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186071</v>
+        <v>122186129</v>
       </c>
       <c r="B14" t="n">
-        <v>57490</v>
+        <v>79737</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,37 +1981,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478617</v>
+        <v>478270</v>
       </c>
       <c r="R14" t="n">
-        <v>6954010</v>
+        <v>6954768</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2013,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186069</v>
+        <v>122186131</v>
       </c>
       <c r="B15" t="n">
-        <v>97165</v>
+        <v>79274</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,20 +2083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478619</v>
+        <v>478306</v>
       </c>
       <c r="R15" t="n">
-        <v>6954010</v>
+        <v>6954783</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2110,12 +2141,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186179</v>
+        <v>122186114</v>
       </c>
       <c r="B16" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,6 +2191,11 @@
       <c r="E16" t="n">
         <v>221945</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -2177,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478474</v>
+        <v>478405</v>
       </c>
       <c r="R16" t="n">
-        <v>6954539</v>
+        <v>6954494</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2207,12 +2243,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186133</v>
+        <v>122186069</v>
       </c>
       <c r="B17" t="n">
-        <v>57532</v>
+        <v>97178</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,20 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478327</v>
+        <v>478619</v>
       </c>
       <c r="R17" t="n">
-        <v>6954735</v>
+        <v>6954010</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2304,12 +2345,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2336,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186114</v>
+        <v>122186071</v>
       </c>
       <c r="B18" t="n">
-        <v>97165</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,29 +2393,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>103031</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478405</v>
+        <v>478617</v>
       </c>
       <c r="R18" t="n">
-        <v>6954494</v>
+        <v>6954010</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2433,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186068</v>
+        <v>122186112</v>
       </c>
       <c r="B19" t="n">
-        <v>90831</v>
+        <v>57536</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,16 +2499,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478648</v>
+        <v>478385</v>
       </c>
       <c r="R19" t="n">
-        <v>6954030</v>
+        <v>6954495</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2530,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186073</v>
+        <v>122186070</v>
       </c>
       <c r="B20" t="n">
-        <v>57532</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,16 +2601,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478615</v>
+        <v>478610</v>
       </c>
       <c r="R20" t="n">
-        <v>6954027</v>
+        <v>6954005</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2627,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186080</v>
+        <v>122186134</v>
       </c>
       <c r="B21" t="n">
-        <v>78388</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,20 +2699,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>103031</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478458</v>
+        <v>478295</v>
       </c>
       <c r="R21" t="n">
-        <v>6954184</v>
+        <v>6954784</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2692,12 +2757,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2727,7 +2792,7 @@
         <v>122186072</v>
       </c>
       <c r="B22" t="n">
-        <v>90831</v>
+        <v>90844</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,6 +2806,11 @@
       </c>
       <c r="E22" t="n">
         <v>5432</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2821,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186078</v>
+        <v>122186080</v>
       </c>
       <c r="B23" t="n">
-        <v>57532</v>
+        <v>78392</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2837,16 +2907,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2856,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478486</v>
+        <v>478458</v>
       </c>
       <c r="R23" t="n">
-        <v>6954106</v>
+        <v>6954184</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2921,7 +2996,7 @@
         <v>122186077</v>
       </c>
       <c r="B24" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,6 +3010,11 @@
       </c>
       <c r="E24" t="n">
         <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3018,7 +3098,7 @@
         <v>122186074</v>
       </c>
       <c r="B25" t="n">
-        <v>96076</v>
+        <v>96089</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3032,6 +3112,11 @@
       </c>
       <c r="E25" t="n">
         <v>990</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Liten hornflikmossa</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3112,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122186081</v>
+        <v>122186135</v>
       </c>
       <c r="B26" t="n">
-        <v>57395</v>
+        <v>57383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3128,11 +3213,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3147,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478413</v>
+        <v>478310</v>
       </c>
       <c r="R26" t="n">
-        <v>6954437</v>
+        <v>6954795</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3177,12 +3267,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3209,10 +3299,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186131</v>
+        <v>122186078</v>
       </c>
       <c r="B27" t="n">
-        <v>79270</v>
+        <v>57536</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3225,16 +3315,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3244,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478306</v>
+        <v>478486</v>
       </c>
       <c r="R27" t="n">
-        <v>6954783</v>
+        <v>6954106</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3274,12 +3369,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3306,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122186134</v>
+        <v>122186081</v>
       </c>
       <c r="B28" t="n">
-        <v>57490</v>
+        <v>57399</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3318,15 +3413,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3341,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478295</v>
+        <v>478413</v>
       </c>
       <c r="R28" t="n">
-        <v>6954784</v>
+        <v>6954437</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3371,12 +3471,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3403,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186112</v>
+        <v>122186073</v>
       </c>
       <c r="B29" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3421,6 +3521,11 @@
       <c r="E29" t="n">
         <v>103021</v>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -3438,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478385</v>
+        <v>478615</v>
       </c>
       <c r="R29" t="n">
-        <v>6954495</v>
+        <v>6954027</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3500,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122186135</v>
+        <v>122186179</v>
       </c>
       <c r="B30" t="n">
-        <v>57379</v>
+        <v>97178</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3512,20 +3617,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3535,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478310</v>
+        <v>478474</v>
       </c>
       <c r="R30" t="n">
-        <v>6954795</v>
+        <v>6954539</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122186089</v>
+        <v>122186133</v>
       </c>
       <c r="B9" t="n">
-        <v>78392</v>
+        <v>57536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478467</v>
+        <v>478327</v>
       </c>
       <c r="R9" t="n">
-        <v>6954372</v>
+        <v>6954735</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186067</v>
+        <v>122186132</v>
       </c>
       <c r="B10" t="n">
-        <v>90844</v>
+        <v>78301</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478696</v>
+        <v>478306</v>
       </c>
       <c r="R10" t="n">
-        <v>6954019</v>
+        <v>6954782</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186132</v>
+        <v>122186089</v>
       </c>
       <c r="B11" t="n">
-        <v>78301</v>
+        <v>78392</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478306</v>
+        <v>478467</v>
       </c>
       <c r="R11" t="n">
-        <v>6954782</v>
+        <v>6954372</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186133</v>
+        <v>122186081</v>
       </c>
       <c r="B12" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478327</v>
+        <v>478413</v>
       </c>
       <c r="R12" t="n">
-        <v>6954735</v>
+        <v>6954437</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186068</v>
+        <v>122186112</v>
       </c>
       <c r="B13" t="n">
-        <v>90844</v>
+        <v>57536</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478648</v>
+        <v>478385</v>
       </c>
       <c r="R13" t="n">
-        <v>6954030</v>
+        <v>6954495</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186129</v>
+        <v>122186078</v>
       </c>
       <c r="B14" t="n">
-        <v>79737</v>
+        <v>57536</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478270</v>
+        <v>478486</v>
       </c>
       <c r="R14" t="n">
-        <v>6954768</v>
+        <v>6954106</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186131</v>
+        <v>122186114</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>97191</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,25 +2083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478306</v>
+        <v>478405</v>
       </c>
       <c r="R15" t="n">
-        <v>6954783</v>
+        <v>6954494</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186114</v>
+        <v>122186179</v>
       </c>
       <c r="B16" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478405</v>
+        <v>478474</v>
       </c>
       <c r="R16" t="n">
-        <v>6954494</v>
+        <v>6954539</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186069</v>
+        <v>122186077</v>
       </c>
       <c r="B17" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478619</v>
+        <v>478526</v>
       </c>
       <c r="R17" t="n">
-        <v>6954010</v>
+        <v>6953974</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186071</v>
+        <v>122186073</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>57536</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2389,42 +2389,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478617</v>
+        <v>478615</v>
       </c>
       <c r="R18" t="n">
-        <v>6954010</v>
+        <v>6954027</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2483,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186112</v>
+        <v>122186068</v>
       </c>
       <c r="B19" t="n">
-        <v>57536</v>
+        <v>90857</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478385</v>
+        <v>478648</v>
       </c>
       <c r="R19" t="n">
-        <v>6954495</v>
+        <v>6954030</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2585,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186070</v>
+        <v>122186080</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>78392</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2625,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478610</v>
+        <v>478458</v>
       </c>
       <c r="R20" t="n">
-        <v>6954005</v>
+        <v>6954184</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2687,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186134</v>
+        <v>122186071</v>
       </c>
       <c r="B21" t="n">
         <v>57494</v>
@@ -2720,17 +2716,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478295</v>
+        <v>478617</v>
       </c>
       <c r="R21" t="n">
-        <v>6954784</v>
+        <v>6954010</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2792,7 +2792,7 @@
         <v>122186072</v>
       </c>
       <c r="B22" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186080</v>
+        <v>122186134</v>
       </c>
       <c r="B23" t="n">
-        <v>78392</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,25 +2903,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478458</v>
+        <v>478295</v>
       </c>
       <c r="R23" t="n">
-        <v>6954184</v>
+        <v>6954784</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2961,12 +2961,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122186077</v>
+        <v>122186067</v>
       </c>
       <c r="B24" t="n">
-        <v>97178</v>
+        <v>90857</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,25 +3005,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478526</v>
+        <v>478696</v>
       </c>
       <c r="R24" t="n">
-        <v>6953974</v>
+        <v>6954019</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3095,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122186074</v>
+        <v>122186070</v>
       </c>
       <c r="B25" t="n">
-        <v>96089</v>
+        <v>57399</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,25 +3107,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>990</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478574</v>
+        <v>478610</v>
       </c>
       <c r="R25" t="n">
-        <v>6954036</v>
+        <v>6954005</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122186135</v>
+        <v>122186069</v>
       </c>
       <c r="B26" t="n">
-        <v>57383</v>
+        <v>97191</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,25 +3209,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478310</v>
+        <v>478619</v>
       </c>
       <c r="R26" t="n">
-        <v>6954795</v>
+        <v>6954010</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3267,12 +3267,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3299,10 +3299,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186078</v>
+        <v>122186074</v>
       </c>
       <c r="B27" t="n">
-        <v>57536</v>
+        <v>96102</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,25 +3311,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>990</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478486</v>
+        <v>478574</v>
       </c>
       <c r="R27" t="n">
-        <v>6954106</v>
+        <v>6954036</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122186081</v>
+        <v>122186131</v>
       </c>
       <c r="B28" t="n">
-        <v>57399</v>
+        <v>79274</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478413</v>
+        <v>478306</v>
       </c>
       <c r="R28" t="n">
-        <v>6954437</v>
+        <v>6954783</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186073</v>
+        <v>122186135</v>
       </c>
       <c r="B29" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478615</v>
+        <v>478310</v>
       </c>
       <c r="R29" t="n">
-        <v>6954027</v>
+        <v>6954795</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3605,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122186179</v>
+        <v>122186129</v>
       </c>
       <c r="B30" t="n">
-        <v>97178</v>
+        <v>79737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3617,25 +3617,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478474</v>
+        <v>478270</v>
       </c>
       <c r="R30" t="n">
-        <v>6954539</v>
+        <v>6954768</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 22356-2024 artfynd.xlsx
+++ b/artfynd/A 22356-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122186133</v>
+        <v>122186072</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
+        <v>90857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478327</v>
+        <v>478577</v>
       </c>
       <c r="R9" t="n">
-        <v>6954735</v>
+        <v>6954027</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122186132</v>
+        <v>122186179</v>
       </c>
       <c r="B10" t="n">
-        <v>78301</v>
+        <v>97191</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478306</v>
+        <v>478474</v>
       </c>
       <c r="R10" t="n">
-        <v>6954782</v>
+        <v>6954539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122186089</v>
+        <v>122186077</v>
       </c>
       <c r="B11" t="n">
-        <v>78392</v>
+        <v>97191</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478467</v>
+        <v>478526</v>
       </c>
       <c r="R11" t="n">
-        <v>6954372</v>
+        <v>6953974</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122186081</v>
+        <v>122186132</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>78301</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478413</v>
+        <v>478306</v>
       </c>
       <c r="R12" t="n">
-        <v>6954437</v>
+        <v>6954782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122186112</v>
+        <v>122186069</v>
       </c>
       <c r="B13" t="n">
-        <v>57536</v>
+        <v>97191</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,25 +1879,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478385</v>
+        <v>478619</v>
       </c>
       <c r="R13" t="n">
-        <v>6954495</v>
+        <v>6954010</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122186078</v>
+        <v>122186133</v>
       </c>
       <c r="B14" t="n">
         <v>57536</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478486</v>
+        <v>478327</v>
       </c>
       <c r="R14" t="n">
-        <v>6954106</v>
+        <v>6954735</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122186114</v>
+        <v>122186081</v>
       </c>
       <c r="B15" t="n">
-        <v>97191</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,25 +2083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478405</v>
+        <v>478413</v>
       </c>
       <c r="R15" t="n">
-        <v>6954494</v>
+        <v>6954437</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122186179</v>
+        <v>122186080</v>
       </c>
       <c r="B16" t="n">
-        <v>97191</v>
+        <v>78392</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,25 +2185,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478474</v>
+        <v>478458</v>
       </c>
       <c r="R16" t="n">
-        <v>6954539</v>
+        <v>6954184</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122186077</v>
+        <v>122186073</v>
       </c>
       <c r="B17" t="n">
-        <v>97191</v>
+        <v>57536</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478526</v>
+        <v>478615</v>
       </c>
       <c r="R17" t="n">
-        <v>6953974</v>
+        <v>6954027</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122186073</v>
+        <v>122186129</v>
       </c>
       <c r="B18" t="n">
-        <v>57536</v>
+        <v>79737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478615</v>
+        <v>478270</v>
       </c>
       <c r="R18" t="n">
-        <v>6954027</v>
+        <v>6954768</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122186068</v>
+        <v>122186070</v>
       </c>
       <c r="B19" t="n">
-        <v>90857</v>
+        <v>57399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478648</v>
+        <v>478610</v>
       </c>
       <c r="R19" t="n">
-        <v>6954030</v>
+        <v>6954005</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2581,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122186080</v>
+        <v>122186089</v>
       </c>
       <c r="B20" t="n">
         <v>78392</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478458</v>
+        <v>478467</v>
       </c>
       <c r="R20" t="n">
-        <v>6954184</v>
+        <v>6954372</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122186071</v>
+        <v>122186067</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>90857</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2695,42 +2695,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478617</v>
+        <v>478696</v>
       </c>
       <c r="R21" t="n">
-        <v>6954010</v>
+        <v>6954019</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2789,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122186072</v>
+        <v>122186068</v>
       </c>
       <c r="B22" t="n">
         <v>90857</v>
@@ -2829,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478577</v>
+        <v>478648</v>
       </c>
       <c r="R22" t="n">
-        <v>6954027</v>
+        <v>6954030</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2891,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122186134</v>
+        <v>122186078</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>57536</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,25 +2899,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2931,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478295</v>
+        <v>478486</v>
       </c>
       <c r="R23" t="n">
-        <v>6954784</v>
+        <v>6954106</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2961,12 +2957,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2993,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122186067</v>
+        <v>122186135</v>
       </c>
       <c r="B24" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3009,21 +3005,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478696</v>
+        <v>478310</v>
       </c>
       <c r="R24" t="n">
-        <v>6954019</v>
+        <v>6954795</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3063,12 +3059,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3095,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122186070</v>
+        <v>122186074</v>
       </c>
       <c r="B25" t="n">
-        <v>57399</v>
+        <v>96102</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,25 +3103,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>990</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478610</v>
+        <v>478574</v>
       </c>
       <c r="R25" t="n">
-        <v>6954005</v>
+        <v>6954036</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3197,7 +3193,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122186069</v>
+        <v>122186114</v>
       </c>
       <c r="B26" t="n">
         <v>97191</v>
@@ -3237,10 +3233,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478619</v>
+        <v>478405</v>
       </c>
       <c r="R26" t="n">
-        <v>6954010</v>
+        <v>6954494</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3299,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122186074</v>
+        <v>122186131</v>
       </c>
       <c r="B27" t="n">
-        <v>96102</v>
+        <v>79274</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,25 +3307,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>990</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3339,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478574</v>
+        <v>478306</v>
       </c>
       <c r="R27" t="n">
-        <v>6954036</v>
+        <v>6954783</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3369,12 +3365,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3401,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122186131</v>
+        <v>122186071</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,38 +3409,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478306</v>
+        <v>478617</v>
       </c>
       <c r="R28" t="n">
-        <v>6954783</v>
+        <v>6954010</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122186135</v>
+        <v>122186134</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>57494</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3515,20 +3515,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478310</v>
+        <v>478295</v>
       </c>
       <c r="R29" t="n">
-        <v>6954795</v>
+        <v>6954784</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122186129</v>
+        <v>122186112</v>
       </c>
       <c r="B30" t="n">
-        <v>79737</v>
+        <v>57536</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3621,21 +3621,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478270</v>
+        <v>478385</v>
       </c>
       <c r="R30" t="n">
-        <v>6954768</v>
+        <v>6954495</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
